--- a/Data_resultados/gemini_manipulative_design.xlsx
+++ b/Data_resultados/gemini_manipulative_design.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,20 +446,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/</t>
+          <t>https://www.temu.com/</t>
         </is>
       </c>
       <c r="B2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'name': 'Cookie Consent with Nudge', 'description': "O banner de consentimento de cookies utiliza linguagem persuasiva ('Help us improve your Mozilla experience') para encorajar a aceitação de cookies adicionais, embora botões claros para 'Accept All Additional Cookies' e 'Reject All Additional Cookies' sejam fornecidos."}, {'name': 'Third-Party Tracking/Analytics', 'description': 'O HTML inclui Google Tag Manager (GTM-MW3R8V) para fins de análise e Sentry para rastreamento de erros (data-sentry-dsn), indicando a coleta de dados e o uso de serviços de terceiros.'}]</t>
+          <t>[{'name': 'Extensive Tracking and Personalization', 'description': "The configuration includes a large list of 'optOutFields' (e.g., gclid, fbclid, ttclid, msclkid) and defines tracking-related cookies (_ttc with ad sub-types). This indicates a significant infrastructure for collecting user data, potentially for highly targeted advertising and personalization. While consent mechanisms are not visible here, extensive, often opaque, data collection can be a manipulative practice."}, {'name': 'Urgency and Scarcity Tactics (Implied)', 'description': "Numerous localStorage keys (e.g., 'mobile.bg.newbie.lowPriceItem.stressCountDownFirstStage', 'DAILY_GIFT_RETAIN_POPUP_FREQUENCY_LIMIT_KEY', 'ATTENDANCE_GIFT_BOX') suggest the implementation of countdowns, limited-time offers, and promotional pop-ups designed to create a sense of urgency or scarcity to pressure users into making immediate purchases or engagements."}, {'name': 'Privacy Maze (Implied)', 'description': "The vast and intricate configuration of privacy settings, including region-specific policies, cookie types, and storage management (e.g., __PRIVACY_CONFIG__ object with numerous regions and cookie definitions), implies a potentially complex privacy control interface. This complexity can make it difficult for users to understand and effectively manage their privacy preferences, resembling a 'privacy maze'."}]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['Dependência de Scripts de Terceiros/CDNs: A inclusão de scripts de domínios externos (transcend-cdn.com e Google Tag Manager) introduz um risco de cadeia de suprimentos. Se esses serviços de terceiros forem comprometidos, a integridade do site da Mozilla poderia ser afetada.', 'Potencial para Abuso do Google Tag Manager: O Google Tag Manager pode ser usado para injetar scripts arbitrários, representando um risco de Cross-Site Scripting (XSS) ou exfiltração de dados se a plataforma for comprometida ou mal configurada.', 'Ausência da Meta Tag Content Security Policy (CSP): Não há meta tag CSP visível no HTML fornecido. Embora uma CSP possa ser entregue via cabeçalhos HTTP, sua ausência explícita no HTML pode aumentar a vulnerabilidade a ataques XSS se os cabeçalhos não estiverem configurados corretamente ou forem removidos.']</t>
+          <t>["**Data Exposure and Attack Surface:** The extensive configuration details, including privacy settings, tracking parameters, and CDN configurations, are exposed in the global 'window' object. While common for client-side configurations, this increases the attack surface. In the event of a successful client-side attack (e.g., XSS), an attacker could easily inspect or potentially manipulate these configurations and access the various tracking parameters and collected data, leading to data exfiltration or other malicious activities.", "**Reliance on Third-Party CDNs:** The configuration for 'window.__CDN_IMG__' shows a reliance on multiple Content Delivery Networks (CDNs) and fallback domains (e.g., kwcdn.com, temucdn.com). While CDNs improve performance, they introduce a supply chain risk. A compromise or misconfiguration of a CDN provider could potentially lead to the injection of malicious content or service disruptions, affecting the integrity and security of the website."]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.trello.com/</t>
+          <t>https://www.google.com/</t>
         </is>
       </c>
       <c r="B3" t="b">
@@ -479,17 +479,67 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[{'name': 'Resource Preloading (Scripts)', 'description': 'Utilização extensiva de `&lt;link rel="preload" as="script"&gt;` para carregar recursos JavaScript antecipadamente, otimizando o tempo de carregamento da página.'}, {'name': 'External Font Loading', 'description': 'Definição de fontes personalizadas via `@font-face` carregadas de um CDN (`assets.ctfassets.net`), o que é comum para manter a identidade visual.'}, {'name': 'CSS-in-JS Framework', 'description': 'Presença do atributo `data-styled="true" data-styled-version="5.3.3"` no bloco `&lt;style&gt;`, indicando o uso de uma biblioteca CSS-in-JS, como styled-components.'}, {'name': 'Standard Meta Tags', 'description': 'Inclusão de meta tags padrão como `charset`, `description` e `viewport` para SEO e responsividade.'}, {'name': 'Favicon', 'description': 'Definição de um ícone de favoritos (`favicon.ico`) para o site.'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['Nenhum risco de segurança óbvio detectado diretamente neste trecho HTML fornecido. Todos os recursos externos (scripts, fontes, favicon) são carregados via HTTPS, o que é uma boa prática de segurança.']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>média</t>
+          <t>baixa</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.pudim.com.br/</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://medium.com/</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>['Falha na conexão ou site inacessível.']</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>baixa</t>
         </is>
       </c>
     </row>
